--- a/src/attributions/attributions_saliency_traj_498.xlsx
+++ b/src/attributions/attributions_saliency_traj_498.xlsx
@@ -999,1140 +999,1140 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.089051230948826e-07</v>
+        <v>1.805348753929138</v>
       </c>
       <c r="B2" t="n">
-        <v>8.053326610024669e-07</v>
+        <v>0.07831990718841553</v>
       </c>
       <c r="C2" t="n">
-        <v>1.380507001158549e-06</v>
+        <v>0.4395164251327515</v>
       </c>
       <c r="D2" t="n">
-        <v>1.005288027045026e-06</v>
+        <v>1.01005494594574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.207039076689398e-06</v>
+        <v>1.071582555770874</v>
       </c>
       <c r="F2" t="n">
-        <v>2.764216162631783e-07</v>
+        <v>0.5085811018943787</v>
       </c>
       <c r="G2" t="n">
-        <v>3.066809028950956e-07</v>
+        <v>0.7143745422363281</v>
       </c>
       <c r="H2" t="n">
-        <v>9.41105156471167e-07</v>
+        <v>0.4245512783527374</v>
       </c>
       <c r="I2" t="n">
-        <v>1.09029906525393e-06</v>
+        <v>0.5147797465324402</v>
       </c>
       <c r="J2" t="n">
-        <v>1.118391196541779e-06</v>
+        <v>1.623775005340576</v>
       </c>
       <c r="K2" t="n">
-        <v>3.335699716444651e-07</v>
+        <v>0.4236285388469696</v>
       </c>
       <c r="L2" t="n">
-        <v>9.977786703530001e-07</v>
+        <v>0.4398999214172363</v>
       </c>
       <c r="M2" t="n">
-        <v>8.651029759221274e-08</v>
+        <v>1.851320266723633</v>
       </c>
       <c r="N2" t="n">
-        <v>7.383381444014958e-07</v>
+        <v>0.8221672177314758</v>
       </c>
       <c r="O2" t="n">
-        <v>7.171939842010033e-07</v>
+        <v>0.334030419588089</v>
       </c>
       <c r="P2" t="n">
-        <v>2.078065506339044e-07</v>
+        <v>0.6849792003631592</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.169199990158631e-07</v>
+        <v>0.588401198387146</v>
       </c>
       <c r="R2" t="n">
-        <v>1.02104809229786e-06</v>
+        <v>0.7423086166381836</v>
       </c>
       <c r="S2" t="n">
-        <v>1.283908090954355e-09</v>
+        <v>0.1787652671337128</v>
       </c>
       <c r="T2" t="n">
-        <v>5.693678986062878e-07</v>
+        <v>0.07760845869779587</v>
       </c>
       <c r="U2" t="n">
-        <v>1.548960852915116e-07</v>
+        <v>0.1839123517274857</v>
       </c>
       <c r="V2" t="n">
-        <v>5.01625095239433e-07</v>
+        <v>0.09753993898630142</v>
       </c>
       <c r="W2" t="n">
-        <v>6.0182046013324e-09</v>
+        <v>0.06590836495161057</v>
       </c>
       <c r="X2" t="n">
-        <v>1.250890136361704e-06</v>
+        <v>0.8631096482276917</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.461272513050062e-07</v>
+        <v>0.1004320383071899</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.259412378360139e-07</v>
+        <v>0.03304784744977951</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.482625660604754e-08</v>
+        <v>0.1244266256690025</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.427477229754004e-07</v>
+        <v>0.1839927732944489</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.179324939926119e-07</v>
+        <v>0.2437753975391388</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.858420048023618e-08</v>
+        <v>0.05125260353088379</v>
       </c>
       <c r="AE2" t="n">
-        <v>9.713905768649056e-08</v>
+        <v>0.06786942481994629</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.480157731582949e-08</v>
+        <v>0.3062531352043152</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.10738322090765e-07</v>
+        <v>0.01272674929350615</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.540925490597147e-07</v>
+        <v>0.09304056316614151</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.09831397216476e-07</v>
+        <v>0.1682580262422562</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8.691353627909848e-07</v>
+        <v>0.4508938789367676</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.911543894399074e-07</v>
+        <v>0.1620579063892365</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.21287803267478e-06</v>
+        <v>0.07565277069807053</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.184063549430903e-07</v>
+        <v>0.09050685167312622</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.027725364925573e-07</v>
+        <v>0.2057643234729767</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.588416343016434e-07</v>
+        <v>0.05163616687059402</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.846187605129671e-07</v>
+        <v>0.6372159719467163</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.395807771586988e-07</v>
+        <v>0.3104341626167297</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.924198779259314e-07</v>
+        <v>0.2076160907745361</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.996668051011511e-07</v>
+        <v>0.159565657377243</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.186326497621849e-08</v>
+        <v>0.6283982396125793</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.19460537462146e-06</v>
+        <v>0.2882399559020996</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.848224883360672e-06</v>
+        <v>0.2614957690238953</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.41252473390341e-07</v>
+        <v>1.088562488555908</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.490480255801231e-06</v>
+        <v>0.8875729441642761</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.093959422694752e-07</v>
+        <v>0.05336799100041389</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.413107580423457e-08</v>
+        <v>0.07987973093986511</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.23518758402497e-07</v>
+        <v>0.003004498779773712</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.320272293829476e-07</v>
+        <v>0.3376959562301636</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.474109012633562e-07</v>
+        <v>0.7529451847076416</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.797910370754835e-07</v>
+        <v>0.4678164124488831</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.362147372674372e-06</v>
+        <v>0.07471740990877151</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.217049145907367e-07</v>
+        <v>0.5719984769821167</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.298743768529675e-06</v>
+        <v>0.08263832330703735</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.039922019837832e-07</v>
+        <v>0.3567199110984802</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.178318254664191e-07</v>
+        <v>0.6601899862289429</v>
       </c>
       <c r="BJ2" t="n">
-        <v>7.301866276065994e-07</v>
+        <v>0.4287479519844055</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.317755732088699e-06</v>
+        <v>0.1519618332386017</v>
       </c>
       <c r="BL2" t="n">
-        <v>5.313885935720464e-07</v>
+        <v>0.1979967504739761</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.08029053080827e-06</v>
+        <v>0.08455377817153931</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.962742087220249e-07</v>
+        <v>0.2723629474639893</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.709652449084388e-07</v>
+        <v>0.4422746896743774</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.193271128220658e-07</v>
+        <v>0.4333246350288391</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.45426417930139e-06</v>
+        <v>0.2158393114805222</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.642339952923066e-08</v>
+        <v>0.09837305545806885</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.82374389321194e-07</v>
+        <v>0.08213409781455994</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.19932427778258e-07</v>
+        <v>0.2536785006523132</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.180725798301864e-07</v>
+        <v>0.1030956506729126</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.057963327701145e-07</v>
+        <v>0.02396668493747711</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.421047208325035e-07</v>
+        <v>0.1305601894855499</v>
       </c>
       <c r="BX2" t="n">
-        <v>4.514459917004388e-08</v>
+        <v>0.6934763193130493</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.538748493767343e-07</v>
+        <v>0.4484003186225891</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.35234574322385e-07</v>
+        <v>0.3215113580226898</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.65071906319281e-07</v>
+        <v>0.009345607832074165</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.762139269587351e-07</v>
+        <v>0.08940675854682922</v>
       </c>
       <c r="CC2" t="n">
-        <v>6.611405751755228e-07</v>
+        <v>0.1657598316669464</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.049637544132565e-07</v>
+        <v>0.4371678829193115</v>
       </c>
       <c r="CE2" t="n">
-        <v>6.912874823683524e-07</v>
+        <v>0.1570943892002106</v>
       </c>
       <c r="CF2" t="n">
-        <v>6.826665810422128e-08</v>
+        <v>0.0817401260137558</v>
       </c>
       <c r="CG2" t="n">
-        <v>4.611612780536234e-08</v>
+        <v>0.5546314120292664</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.370663795796645e-07</v>
+        <v>0.1233984306454659</v>
       </c>
       <c r="CI2" t="n">
-        <v>5.628583608086046e-07</v>
+        <v>0.4399593472480774</v>
       </c>
       <c r="CJ2" t="n">
-        <v>3.56272877866104e-08</v>
+        <v>0.05336068570613861</v>
       </c>
       <c r="CK2" t="n">
-        <v>6.191858403781225e-08</v>
+        <v>0.1329400539398193</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.419052608753191e-07</v>
+        <v>0.03269755095243454</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.532217647261859e-07</v>
+        <v>0.1427805423736572</v>
       </c>
       <c r="CN2" t="n">
-        <v>5.761768306911108e-08</v>
+        <v>1.103679418563843</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.585953327776224e-06</v>
+        <v>0.3800738751888275</v>
       </c>
       <c r="CP2" t="n">
-        <v>5.557802751354757e-07</v>
+        <v>0.9274054765701294</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.628826448220934e-07</v>
+        <v>0.3286307454109192</v>
       </c>
       <c r="CR2" t="n">
-        <v>7.459489665961883e-07</v>
+        <v>0.3755306601524353</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.990782033724827e-07</v>
+        <v>0.2232494354248047</v>
       </c>
       <c r="CT2" t="n">
-        <v>6.197516313477536e-07</v>
+        <v>0.2631364464759827</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.135390562012617e-06</v>
+        <v>0.2205531150102615</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.349949141944307e-07</v>
+        <v>0.4637764096260071</v>
       </c>
       <c r="CW2" t="n">
-        <v>4.530272974534455e-07</v>
+        <v>0.145709216594696</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.761210057793505e-07</v>
+        <v>0.1190700829029083</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.609751762998712e-07</v>
+        <v>0.5511887073516846</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.513653131723913e-07</v>
+        <v>0.2755844593048096</v>
       </c>
       <c r="DA2" t="n">
-        <v>4.966707933817816e-07</v>
+        <v>0.3995281159877777</v>
       </c>
       <c r="DB2" t="n">
-        <v>3.336157661237849e-08</v>
+        <v>0.08641549944877625</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.822811140390513e-08</v>
+        <v>0.1520312428474426</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.67783002275246e-07</v>
+        <v>0.03922922909259796</v>
       </c>
       <c r="DE2" t="n">
-        <v>7.632844756244594e-08</v>
+        <v>0.675389289855957</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.175982333734282e-06</v>
+        <v>0.4108824133872986</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.489552116458071e-06</v>
+        <v>0.1533450037240982</v>
       </c>
       <c r="DH2" t="n">
-        <v>5.8129091939918e-07</v>
+        <v>0.3018897175788879</v>
       </c>
       <c r="DI2" t="n">
-        <v>3.55683482666791e-07</v>
+        <v>0.2738336622714996</v>
       </c>
       <c r="DJ2" t="n">
-        <v>8.90237572548358e-09</v>
+        <v>0.06337766349315643</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.133975543638371e-08</v>
+        <v>0.296343207359314</v>
       </c>
       <c r="DL2" t="n">
-        <v>3.158232402711292e-06</v>
+        <v>0.6817046403884888</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.615059886717063e-06</v>
+        <v>0.1158237382769585</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.945755201404609e-07</v>
+        <v>0.4647952914237976</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.343284793620114e-06</v>
+        <v>0.04441465809941292</v>
       </c>
       <c r="DP2" t="n">
-        <v>4.810593168258492e-07</v>
+        <v>0.03528237342834473</v>
       </c>
       <c r="DQ2" t="n">
-        <v>4.064029468509034e-08</v>
+        <v>0.1677289456129074</v>
       </c>
       <c r="DR2" t="n">
-        <v>1.276055058951897e-06</v>
+        <v>0.7519716024398804</v>
       </c>
       <c r="DS2" t="n">
-        <v>2.972037691506557e-07</v>
+        <v>0.3338159024715424</v>
       </c>
       <c r="DT2" t="n">
-        <v>1.396256621433167e-08</v>
+        <v>0.1271393746137619</v>
       </c>
       <c r="DU2" t="n">
-        <v>1.113065195568197e-08</v>
+        <v>0.3443455994129181</v>
       </c>
       <c r="DV2" t="n">
-        <v>5.283731638883182e-07</v>
+        <v>0.5080145597457886</v>
       </c>
       <c r="DW2" t="n">
-        <v>1.936843574412705e-07</v>
+        <v>0.04480914771556854</v>
       </c>
       <c r="DX2" t="n">
-        <v>4.386969862935075e-07</v>
+        <v>0.4273461103439331</v>
       </c>
       <c r="DY2" t="n">
-        <v>1.092254731105413e-08</v>
+        <v>0.2601989507675171</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.287325517296267e-07</v>
+        <v>0.1707173883914948</v>
       </c>
       <c r="EA2" t="n">
-        <v>6.503431109194935e-07</v>
+        <v>0.1303778439760208</v>
       </c>
       <c r="EB2" t="n">
-        <v>6.943620292076957e-07</v>
+        <v>0.02547545731067657</v>
       </c>
       <c r="EC2" t="n">
-        <v>5.239046458882513e-07</v>
+        <v>0.1332574784755707</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.100239686024906e-07</v>
+        <v>0.4165571928024292</v>
       </c>
       <c r="EE2" t="n">
-        <v>8.176198775800003e-07</v>
+        <v>0.08666054159402847</v>
       </c>
       <c r="EF2" t="n">
-        <v>1.071017265985574e-07</v>
+        <v>0.4640078246593475</v>
       </c>
       <c r="EG2" t="n">
-        <v>1.850325475061254e-06</v>
+        <v>0.2831525206565857</v>
       </c>
       <c r="EH2" t="n">
-        <v>5.247462695479044e-07</v>
+        <v>0.3644967675209045</v>
       </c>
       <c r="EI2" t="n">
-        <v>6.13075258115714e-07</v>
+        <v>0.5218163132667542</v>
       </c>
       <c r="EJ2" t="n">
-        <v>4.480541804241511e-07</v>
+        <v>0.2846940755844116</v>
       </c>
       <c r="EK2" t="n">
-        <v>1.451928255846724e-06</v>
+        <v>0.511004626750946</v>
       </c>
       <c r="EL2" t="n">
-        <v>5.236450917323054e-08</v>
+        <v>0.03930234163999557</v>
       </c>
       <c r="EM2" t="n">
-        <v>1.844484813773306e-07</v>
+        <v>0.03218758106231689</v>
       </c>
       <c r="EN2" t="n">
-        <v>3.467153533165401e-07</v>
+        <v>0.02514214068651199</v>
       </c>
       <c r="EO2" t="n">
-        <v>4.290657784622454e-07</v>
+        <v>0.08956929296255112</v>
       </c>
       <c r="EP2" t="n">
-        <v>1.225135406457412e-06</v>
+        <v>0.07305438816547394</v>
       </c>
       <c r="EQ2" t="n">
-        <v>3.81407005534129e-07</v>
+        <v>0.08974286913871765</v>
       </c>
       <c r="ER2" t="n">
-        <v>1.779604019702674e-08</v>
+        <v>0.4486362040042877</v>
       </c>
       <c r="ES2" t="n">
-        <v>5.720253852814494e-07</v>
+        <v>0.4500831663608551</v>
       </c>
       <c r="ET2" t="n">
-        <v>2.348162269072418e-07</v>
+        <v>0.4886507987976074</v>
       </c>
       <c r="EU2" t="n">
-        <v>2.242722985101864e-07</v>
+        <v>0.2476346790790558</v>
       </c>
       <c r="EV2" t="n">
-        <v>3.635973939708492e-07</v>
+        <v>0.04605816677212715</v>
       </c>
       <c r="EW2" t="n">
-        <v>3.754068416128575e-07</v>
+        <v>0.1067392751574516</v>
       </c>
       <c r="EX2" t="n">
-        <v>3.169605804487219e-07</v>
+        <v>0.3868771195411682</v>
       </c>
       <c r="EY2" t="n">
-        <v>5.140867074260314e-07</v>
+        <v>0.1442663371562958</v>
       </c>
       <c r="EZ2" t="n">
-        <v>1.208078401759849e-07</v>
+        <v>0.1027296259999275</v>
       </c>
       <c r="FA2" t="n">
-        <v>7.917712707694591e-08</v>
+        <v>0.5500407218933105</v>
       </c>
       <c r="FB2" t="n">
-        <v>2.375628938011687e-08</v>
+        <v>0.1619016081094742</v>
       </c>
       <c r="FC2" t="n">
-        <v>4.45499608758837e-07</v>
+        <v>0.3118915557861328</v>
       </c>
       <c r="FD2" t="n">
-        <v>4.086135518832634e-08</v>
+        <v>0.1104300618171692</v>
       </c>
       <c r="FE2" t="n">
-        <v>1.764624073530285e-07</v>
+        <v>0.06933669745922089</v>
       </c>
       <c r="FF2" t="n">
-        <v>1.634078756751478e-07</v>
+        <v>0.08351594209671021</v>
       </c>
       <c r="FG2" t="n">
-        <v>6.732081914151422e-08</v>
+        <v>0.3301961421966553</v>
       </c>
       <c r="FH2" t="n">
-        <v>4.678804543800652e-08</v>
+        <v>0.527904212474823</v>
       </c>
       <c r="FI2" t="n">
-        <v>6.896391369082266e-07</v>
+        <v>0.1689310669898987</v>
       </c>
       <c r="FJ2" t="n">
-        <v>2.469446087616234e-07</v>
+        <v>0.6900807619094849</v>
       </c>
       <c r="FK2" t="n">
-        <v>2.086875383611186e-07</v>
+        <v>0.2066218703985214</v>
       </c>
       <c r="FL2" t="n">
-        <v>2.838392560988723e-07</v>
+        <v>0.3255361914634705</v>
       </c>
       <c r="FM2" t="n">
-        <v>1.846205179845128e-07</v>
+        <v>0.04220210388302803</v>
       </c>
       <c r="FN2" t="n">
-        <v>3.066781175675715e-07</v>
+        <v>0.2832817435264587</v>
       </c>
       <c r="FO2" t="n">
-        <v>5.896210808487012e-08</v>
+        <v>0.4060001075267792</v>
       </c>
       <c r="FP2" t="n">
-        <v>5.598084840130468e-08</v>
+        <v>0.1323522329330444</v>
       </c>
       <c r="FQ2" t="n">
-        <v>6.726265269207943e-07</v>
+        <v>0.2257534712553024</v>
       </c>
       <c r="FR2" t="n">
-        <v>2.760918960120762e-07</v>
+        <v>0.4895585179328918</v>
       </c>
       <c r="FS2" t="n">
-        <v>2.520935140637448e-07</v>
+        <v>0.5403099060058594</v>
       </c>
       <c r="FT2" t="n">
-        <v>1.214608573718579e-06</v>
+        <v>0.588346540927887</v>
       </c>
       <c r="FU2" t="n">
-        <v>4.146104970459419e-07</v>
+        <v>0.4741821885108948</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.107304328229475e-07</v>
+        <v>0.1643224507570267</v>
       </c>
       <c r="FW2" t="n">
-        <v>7.975422704475932e-07</v>
+        <v>0.1897384375333786</v>
       </c>
       <c r="FX2" t="n">
-        <v>1.207971990879741e-06</v>
+        <v>0.0008079418912529945</v>
       </c>
       <c r="FY2" t="n">
-        <v>4.176984020887176e-07</v>
+        <v>0.292217493057251</v>
       </c>
       <c r="FZ2" t="n">
-        <v>1.355893601839853e-07</v>
+        <v>1.104699611663818</v>
       </c>
       <c r="GA2" t="n">
-        <v>6.560015322065738e-07</v>
+        <v>0.0724562481045723</v>
       </c>
       <c r="GB2" t="n">
-        <v>5.614477913695737e-07</v>
+        <v>0.2414137423038483</v>
       </c>
       <c r="GC2" t="n">
-        <v>4.29296875381624e-07</v>
+        <v>0.3811958134174347</v>
       </c>
       <c r="GD2" t="n">
-        <v>2.041853349510347e-06</v>
+        <v>0.5344101190567017</v>
       </c>
       <c r="GE2" t="n">
-        <v>6.265531737881247e-08</v>
+        <v>0.4065001010894775</v>
       </c>
       <c r="GF2" t="n">
-        <v>6.636099101342552e-07</v>
+        <v>0.1123227402567863</v>
       </c>
       <c r="GG2" t="n">
-        <v>3.58435357838971e-07</v>
+        <v>0.0723264291882515</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2.064320043057339e-17</v>
+        <v>0.009722981601953506</v>
       </c>
       <c r="B3" t="n">
-        <v>4.986912680814287e-19</v>
+        <v>0.0007148505537770689</v>
       </c>
       <c r="C3" t="n">
-        <v>4.867791951764174e-19</v>
+        <v>0.007396080531179905</v>
       </c>
       <c r="D3" t="n">
-        <v>8.221942127241932e-19</v>
+        <v>0.002223212271928787</v>
       </c>
       <c r="E3" t="n">
-        <v>2.143067285820627e-19</v>
+        <v>0.004802870564162731</v>
       </c>
       <c r="F3" t="n">
-        <v>2.663546387839126e-17</v>
+        <v>0.01275796629488468</v>
       </c>
       <c r="G3" t="n">
-        <v>2.818981379756082e-19</v>
+        <v>0.001923077274113894</v>
       </c>
       <c r="H3" t="n">
-        <v>3.127828803594727e-18</v>
+        <v>0.004796778783202171</v>
       </c>
       <c r="I3" t="n">
-        <v>1.596964196376766e-18</v>
+        <v>0.00121342099737376</v>
       </c>
       <c r="J3" t="n">
-        <v>1.311793473403957e-17</v>
+        <v>0.014777603559196</v>
       </c>
       <c r="K3" t="n">
-        <v>4.319661235843793e-20</v>
+        <v>0.001165393274277449</v>
       </c>
       <c r="L3" t="n">
-        <v>3.739865115496694e-18</v>
+        <v>0.008284803479909897</v>
       </c>
       <c r="M3" t="n">
-        <v>9.952333141362916e-19</v>
+        <v>0.002558019012212753</v>
       </c>
       <c r="N3" t="n">
-        <v>1.332228556846773e-18</v>
+        <v>0.003168411552906036</v>
       </c>
       <c r="O3" t="n">
-        <v>1.903689839905666e-17</v>
+        <v>0.01647304929792881</v>
       </c>
       <c r="P3" t="n">
-        <v>1.759799249451199e-18</v>
+        <v>0.000228396849706769</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.954037628139286e-18</v>
+        <v>0.008080991916358471</v>
       </c>
       <c r="R3" t="n">
-        <v>9.581100686303711e-19</v>
+        <v>0.004318314604461193</v>
       </c>
       <c r="S3" t="n">
-        <v>4.550879310157985e-18</v>
+        <v>0.0005221370374783874</v>
       </c>
       <c r="T3" t="n">
-        <v>6.359939026243095e-18</v>
+        <v>0.003290613880380988</v>
       </c>
       <c r="U3" t="n">
-        <v>1.457116492525183e-18</v>
+        <v>0.002366284839808941</v>
       </c>
       <c r="V3" t="n">
-        <v>1.482428012474152e-18</v>
+        <v>5.325302481651306e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>4.107008816788049e-18</v>
+        <v>0.00065716722747311</v>
       </c>
       <c r="X3" t="n">
-        <v>2.213409174148488e-19</v>
+        <v>0.002387240529060364</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.210750466448461e-18</v>
+        <v>0.0002190692903241143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.311456397304342e-18</v>
+        <v>0.003623784054070711</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.749552526072865e-19</v>
+        <v>0.001448909984901547</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.669755653150793e-18</v>
+        <v>0.006371553987264633</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.53321973963318e-18</v>
+        <v>0.002632467076182365</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.972469602101395e-18</v>
+        <v>9.064524783752859e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.446374253916391e-18</v>
+        <v>0.002741058357059956</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.134182228668465e-18</v>
+        <v>0.0001572481705807149</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.605735297629382e-18</v>
+        <v>0.003493550233542919</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.112590689145428e-18</v>
+        <v>0.0009318764205090702</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.328299184558122e-18</v>
+        <v>0.0008598778513260186</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.425518123771619e-19</v>
+        <v>0.004517119377851486</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.32141704186168e-18</v>
+        <v>0.0006921053281985223</v>
       </c>
       <c r="AL3" t="n">
-        <v>9.963025484755929e-19</v>
+        <v>0.003385663731023669</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.416705238127902e-18</v>
+        <v>0.0009005303145386279</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.821187217840903e-18</v>
+        <v>0.003801696468144655</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.998969194248682e-19</v>
+        <v>0.002365804277360439</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.374410252637147e-19</v>
+        <v>0.00445151561871171</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.311847900457854e-19</v>
+        <v>8.058112871367484e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.524807370387388e-18</v>
+        <v>0.0008157065021805465</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.391050575665838e-19</v>
+        <v>0.0003435637045186013</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.719898284367659e-18</v>
+        <v>0.008290569297969341</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.443175614574725e-18</v>
+        <v>0.005680575035512447</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.095615759788793e-18</v>
+        <v>0.0003598792245611548</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.410813138997277e-18</v>
+        <v>0.0008228473598137498</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.597159801051302e-18</v>
+        <v>0.001892929780296981</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.068061645346941e-17</v>
+        <v>0.01591984368860722</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.776391825072887e-19</v>
+        <v>0.003293570596724749</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.625661193821301e-19</v>
+        <v>0.004077081102877855</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.246889872243159e-18</v>
+        <v>0.0009327445295639336</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.92170659592832e-18</v>
+        <v>0.003220824990421534</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.171153992270037e-17</v>
+        <v>0.004562783520668745</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.410698574482438e-18</v>
+        <v>0.003493592375889421</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.377314632979102e-18</v>
+        <v>0.00366314360871911</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.393867907018489e-18</v>
+        <v>0.002004026202484965</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.906958379196806e-18</v>
+        <v>0.004487589467316866</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.827600142334874e-18</v>
+        <v>0.002691065892577171</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.30702059418886e-19</v>
+        <v>0.001647200318984687</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.155402777686772e-19</v>
+        <v>0.002428983571007848</v>
       </c>
       <c r="BL3" t="n">
-        <v>2.116262394673269e-18</v>
+        <v>0.003479323582723737</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.76728190173202e-18</v>
+        <v>0.001052090898156166</v>
       </c>
       <c r="BN3" t="n">
-        <v>6.674185354542296e-18</v>
+        <v>0.004675528034567833</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.213537387143433e-19</v>
+        <v>0.003370100166648626</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.122737771303488e-18</v>
+        <v>0.002312451833859086</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.825326636421272e-18</v>
+        <v>0.002158860210329294</v>
       </c>
       <c r="BR3" t="n">
-        <v>2.574651355359583e-20</v>
+        <v>0.004655466414988041</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.236822785765826e-18</v>
+        <v>0.001781198428943753</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.448108265318994e-19</v>
+        <v>0.001894519082270563</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.528863220185555e-18</v>
+        <v>0.00419372133910656</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.545946418575025e-18</v>
+        <v>0.001012045657262206</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.179730515508391e-18</v>
+        <v>0.002294066362082958</v>
       </c>
       <c r="BX3" t="n">
-        <v>9.661994814308334e-19</v>
+        <v>0.004943246021866798</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.844598290332532e-18</v>
+        <v>0.002207641024142504</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.34093043930696e-18</v>
+        <v>0.009736430831253529</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.893741446530742e-20</v>
+        <v>0.0002952994545921683</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.39878038346516e-18</v>
+        <v>0.003676094114780426</v>
       </c>
       <c r="CC3" t="n">
-        <v>7.041650001911322e-19</v>
+        <v>8.042465196922421e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.120621314538527e-18</v>
+        <v>0.003593231551349163</v>
       </c>
       <c r="CE3" t="n">
-        <v>2.746961090266563e-19</v>
+        <v>0.002196292392909527</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.348695804102454e-18</v>
+        <v>0.00209209811873734</v>
       </c>
       <c r="CG3" t="n">
-        <v>5.460945591437934e-19</v>
+        <v>0.0001589977764524519</v>
       </c>
       <c r="CH3" t="n">
-        <v>4.131742085790055e-19</v>
+        <v>0.0008193350513465703</v>
       </c>
       <c r="CI3" t="n">
-        <v>4.285992503371048e-18</v>
+        <v>0.003543204162269831</v>
       </c>
       <c r="CJ3" t="n">
-        <v>6.581588688821579e-19</v>
+        <v>0.0004491184954531491</v>
       </c>
       <c r="CK3" t="n">
-        <v>2.354008371586576e-18</v>
+        <v>0.0002522395807318389</v>
       </c>
       <c r="CL3" t="n">
-        <v>7.307522394398116e-19</v>
+        <v>8.537317626178265e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.064813369119991e-18</v>
+        <v>0.0003799073165282607</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.128084517571749e-17</v>
+        <v>0.003926926292479038</v>
       </c>
       <c r="CO3" t="n">
-        <v>4.091681987218054e-19</v>
+        <v>0.0007930615684017539</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.611329635279822e-18</v>
+        <v>8.335813618032262e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.602621847387604e-18</v>
+        <v>0.001108461059629917</v>
       </c>
       <c r="CR3" t="n">
-        <v>4.407456531698947e-18</v>
+        <v>0.004150502383708954</v>
       </c>
       <c r="CS3" t="n">
-        <v>7.251238957568477e-19</v>
+        <v>0.003705829149112105</v>
       </c>
       <c r="CT3" t="n">
-        <v>4.886037591523139e-18</v>
+        <v>0.003207576228305697</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.107142579208591e-18</v>
+        <v>0.0002947762259282172</v>
       </c>
       <c r="CV3" t="n">
-        <v>3.780549166744502e-18</v>
+        <v>0.004175564274191856</v>
       </c>
       <c r="CW3" t="n">
-        <v>6.176237101446093e-19</v>
+        <v>0.00242282054387033</v>
       </c>
       <c r="CX3" t="n">
-        <v>3.747093846869794e-18</v>
+        <v>0.00117637193761766</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.343974935135333e-18</v>
+        <v>5.616137059405446e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>5.017022055111218e-19</v>
+        <v>0.0008125742897391319</v>
       </c>
       <c r="DA3" t="n">
-        <v>4.455705976829165e-18</v>
+        <v>0.00348884891718626</v>
       </c>
       <c r="DB3" t="n">
-        <v>6.593512497351531e-19</v>
+        <v>0.0001866673992481083</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.099586226729047e-18</v>
+        <v>0.001044572563841939</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.266701939473442e-18</v>
+        <v>0.0005454565398395061</v>
       </c>
       <c r="DE3" t="n">
-        <v>3.764774005282503e-18</v>
+        <v>0.007360741030424833</v>
       </c>
       <c r="DF3" t="n">
-        <v>5.355787671127716e-19</v>
+        <v>0.001046148943714797</v>
       </c>
       <c r="DG3" t="n">
-        <v>5.165117576850568e-18</v>
+        <v>0.005414166487753391</v>
       </c>
       <c r="DH3" t="n">
-        <v>5.050589044368619e-18</v>
+        <v>0.0006293997867032886</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.697445092747002e-17</v>
+        <v>0.0004584515700116754</v>
       </c>
       <c r="DJ3" t="n">
-        <v>8.665105691380865e-19</v>
+        <v>0.002943039638921618</v>
       </c>
       <c r="DK3" t="n">
-        <v>1.472470283013268e-19</v>
+        <v>0.001236162148416042</v>
       </c>
       <c r="DL3" t="n">
-        <v>2.87140426126936e-18</v>
+        <v>0.0004448424151632935</v>
       </c>
       <c r="DM3" t="n">
-        <v>5.789363488184123e-18</v>
+        <v>0.004620051011443138</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.793732679719962e-18</v>
+        <v>0.0008812044397927821</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.451661534807958e-18</v>
+        <v>0.0002191151725128293</v>
       </c>
       <c r="DP3" t="n">
-        <v>2.664510260047903e-18</v>
+        <v>0.00125416973605752</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.616570190969985e-19</v>
+        <v>0.002151763532310724</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.570601960757907e-18</v>
+        <v>0.0009910298977047205</v>
       </c>
       <c r="DS3" t="n">
-        <v>3.633109082243023e-19</v>
+        <v>0.0008570482023060322</v>
       </c>
       <c r="DT3" t="n">
-        <v>2.341521666649782e-18</v>
+        <v>0.0006775232031941414</v>
       </c>
       <c r="DU3" t="n">
-        <v>3.05953884017388e-18</v>
+        <v>0.002845762530341744</v>
       </c>
       <c r="DV3" t="n">
-        <v>7.804050998768025e-19</v>
+        <v>0.001745859859511256</v>
       </c>
       <c r="DW3" t="n">
-        <v>2.463113907972627e-18</v>
+        <v>0.002569789765402675</v>
       </c>
       <c r="DX3" t="n">
-        <v>2.205486851831761e-18</v>
+        <v>0.0001518662611488253</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.848913874843041e-18</v>
+        <v>0.001718122977763414</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.083943034618289e-18</v>
+        <v>0.004931130446493626</v>
       </c>
       <c r="EA3" t="n">
-        <v>4.657741946313098e-18</v>
+        <v>0.001677948050200939</v>
       </c>
       <c r="EB3" t="n">
-        <v>4.967827969721464e-18</v>
+        <v>0.002113502472639084</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.479993516533832e-18</v>
+        <v>0.0001886332320282236</v>
       </c>
       <c r="ED3" t="n">
-        <v>5.212694730937933e-19</v>
+        <v>0.0003883678582496941</v>
       </c>
       <c r="EE3" t="n">
-        <v>2.702151113822129e-18</v>
+        <v>0.0001024189405143261</v>
       </c>
       <c r="EF3" t="n">
-        <v>2.564123620908468e-18</v>
+        <v>0.001522467122413218</v>
       </c>
       <c r="EG3" t="n">
-        <v>1.021692133594872e-19</v>
+        <v>0.001363720162771642</v>
       </c>
       <c r="EH3" t="n">
-        <v>3.794657972862512e-18</v>
+        <v>0.002602566499263048</v>
       </c>
       <c r="EI3" t="n">
-        <v>2.978708405076423e-18</v>
+        <v>0.001399094355292618</v>
       </c>
       <c r="EJ3" t="n">
-        <v>3.515864605617334e-18</v>
+        <v>0.0006240719230845571</v>
       </c>
       <c r="EK3" t="n">
-        <v>3.121036616789901e-18</v>
+        <v>0.0007972214370965958</v>
       </c>
       <c r="EL3" t="n">
-        <v>8.119807552070595e-19</v>
+        <v>0.0003011589287780225</v>
       </c>
       <c r="EM3" t="n">
-        <v>6.522492837909259e-19</v>
+        <v>0.0006643736851401627</v>
       </c>
       <c r="EN3" t="n">
-        <v>2.320165104004581e-19</v>
+        <v>0.0007057582843117416</v>
       </c>
       <c r="EO3" t="n">
-        <v>2.165930868144322e-18</v>
+        <v>0.003843673039227724</v>
       </c>
       <c r="EP3" t="n">
-        <v>1.390356503044829e-18</v>
+        <v>0.003912389278411865</v>
       </c>
       <c r="EQ3" t="n">
-        <v>5.813358343393062e-18</v>
+        <v>0.0009630568092688918</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.891211365415967e-18</v>
+        <v>0.001960334368050098</v>
       </c>
       <c r="ES3" t="n">
-        <v>6.069188763243462e-18</v>
+        <v>0.0008632065146230161</v>
       </c>
       <c r="ET3" t="n">
-        <v>4.374477254266764e-18</v>
+        <v>0.001158396480605006</v>
       </c>
       <c r="EU3" t="n">
-        <v>9.647611694419686e-20</v>
+        <v>0.0008272582199424505</v>
       </c>
       <c r="EV3" t="n">
-        <v>3.936005768754961e-18</v>
+        <v>2.845015842467546e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>8.87519612528438e-19</v>
+        <v>0.000603902037255466</v>
       </c>
       <c r="EX3" t="n">
-        <v>3.58892864194353e-18</v>
+        <v>0.003898199880495667</v>
       </c>
       <c r="EY3" t="n">
-        <v>1.244465417637933e-18</v>
+        <v>0.001380934496410191</v>
       </c>
       <c r="EZ3" t="n">
-        <v>3.451649954279383e-18</v>
+        <v>0.001545977080240846</v>
       </c>
       <c r="FA3" t="n">
-        <v>1.054537407767821e-18</v>
+        <v>0.001195056363940239</v>
       </c>
       <c r="FB3" t="n">
-        <v>2.826413856053813e-19</v>
+        <v>0.0003217917983420193</v>
       </c>
       <c r="FC3" t="n">
-        <v>4.142108571720511e-18</v>
+        <v>0.00407074112445116</v>
       </c>
       <c r="FD3" t="n">
-        <v>5.981439169117152e-19</v>
+        <v>0.0005765948444604874</v>
       </c>
       <c r="FE3" t="n">
-        <v>2.536402523835131e-18</v>
+        <v>0.0006009804783388972</v>
       </c>
       <c r="FF3" t="n">
-        <v>1.451601058995832e-18</v>
+        <v>0.0005430330638773739</v>
       </c>
       <c r="FG3" t="n">
-        <v>9.66173425241538e-19</v>
+        <v>0.003927654586732388</v>
       </c>
       <c r="FH3" t="n">
-        <v>6.343514114409936e-18</v>
+        <v>0.000483473326312378</v>
       </c>
       <c r="FI3" t="n">
-        <v>4.471284269305376e-18</v>
+        <v>0.0003403597511351109</v>
       </c>
       <c r="FJ3" t="n">
-        <v>3.470444945362659e-18</v>
+        <v>0.001664482289925218</v>
       </c>
       <c r="FK3" t="n">
-        <v>3.667842499561701e-18</v>
+        <v>0.001392142963595688</v>
       </c>
       <c r="FL3" t="n">
-        <v>2.7781952751002e-18</v>
+        <v>0.004228981677442789</v>
       </c>
       <c r="FM3" t="n">
-        <v>6.517823403351398e-19</v>
+        <v>0.0001749454240780324</v>
       </c>
       <c r="FN3" t="n">
-        <v>2.838995945254992e-18</v>
+        <v>0.00296514923684299</v>
       </c>
       <c r="FO3" t="n">
-        <v>3.924301576677642e-18</v>
+        <v>0.001371429301798344</v>
       </c>
       <c r="FP3" t="n">
-        <v>2.504723160735575e-18</v>
+        <v>0.002440281212329865</v>
       </c>
       <c r="FQ3" t="n">
-        <v>6.357328857820184e-18</v>
+        <v>0.0119902053847909</v>
       </c>
       <c r="FR3" t="n">
-        <v>6.991388439941069e-18</v>
+        <v>0.0001009878469631076</v>
       </c>
       <c r="FS3" t="n">
-        <v>6.449229451055438e-19</v>
+        <v>0.005602027289569378</v>
       </c>
       <c r="FT3" t="n">
-        <v>3.899209466386152e-18</v>
+        <v>0.007959472015500069</v>
       </c>
       <c r="FU3" t="n">
-        <v>1.437378929133902e-18</v>
+        <v>0.003789668437093496</v>
       </c>
       <c r="FV3" t="n">
-        <v>1.074818945809433e-18</v>
+        <v>0.002887227572500706</v>
       </c>
       <c r="FW3" t="n">
-        <v>8.709632823754594e-20</v>
+        <v>0.001895738649182022</v>
       </c>
       <c r="FX3" t="n">
-        <v>1.497809332566999e-18</v>
+        <v>0.003945096395909786</v>
       </c>
       <c r="FY3" t="n">
-        <v>2.36150614345391e-18</v>
+        <v>0.004119338002055883</v>
       </c>
       <c r="FZ3" t="n">
-        <v>3.599294455789738e-18</v>
+        <v>0.009006356820464134</v>
       </c>
       <c r="GA3" t="n">
-        <v>2.013206650492278e-19</v>
+        <v>0.0007379331509582698</v>
       </c>
       <c r="GB3" t="n">
-        <v>2.851053757044177e-18</v>
+        <v>0.004671457223594189</v>
       </c>
       <c r="GC3" t="n">
-        <v>5.673266621260775e-18</v>
+        <v>0.004047990310937166</v>
       </c>
       <c r="GD3" t="n">
-        <v>3.436940201446352e-18</v>
+        <v>0.001292333472520113</v>
       </c>
       <c r="GE3" t="n">
-        <v>2.30124065915544e-18</v>
+        <v>0.0002623904147185385</v>
       </c>
       <c r="GF3" t="n">
-        <v>4.662469283513838e-18</v>
+        <v>0.001604211400263011</v>
       </c>
       <c r="GG3" t="n">
-        <v>3.527514203774224e-18</v>
+        <v>0.001951263519003987</v>
       </c>
     </row>
     <row r="4">
